--- a/ALLY_LOTTE_WH/DATA/customer_converted.xlsx
+++ b/ALLY_LOTTE_WH/DATA/customer_converted.xlsx
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E2" t="n">
         <v>480</v>
@@ -499,10 +499,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/07/20                    </t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>2027/07/20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>58852008304911</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -521,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E3" t="n">
         <v>480</v>
@@ -535,10 +539,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/07/20                    </t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>2027/07/20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>58852008304911</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -557,7 +565,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E4" t="n">
         <v>480</v>
@@ -571,10 +579,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/07/20                    </t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>2027/07/20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>58852008304911</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -593,7 +605,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E5" t="n">
         <v>4320</v>
@@ -607,10 +619,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/07/08                    </t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>2027/07/08</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>58852008510510</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -629,7 +645,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
         <v>960</v>
@@ -643,10 +659,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/07/29                    </t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>2027/07/29</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>58852008304898</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -665,7 +685,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E7" t="n">
         <v>2160</v>
@@ -679,10 +699,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/07/29                    </t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>2027/07/29</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>58852008304898</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -701,7 +725,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
         <v>960</v>
@@ -715,10 +739,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/04/06                    </t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>2027/04/06</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>08935341301337</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -737,7 +765,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E9" t="n">
         <v>960</v>
@@ -751,10 +779,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/04/06                    </t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>2027/04/06</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>08935341301337</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -773,7 +805,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
         <v>960</v>
@@ -787,10 +819,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/04/06                    </t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>2027/04/06</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>08935341301337</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -809,7 +845,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
         <v>960</v>
@@ -823,10 +859,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/04/06                    </t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>2027/04/06</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>08935341301337</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -845,7 +885,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E12" t="n">
         <v>960</v>
@@ -859,10 +899,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/04/06                    </t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>2027/04/06</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>08935341301337</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -881,7 +925,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E13" t="n">
         <v>2160</v>
@@ -895,10 +939,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/07/29                    </t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>2027/07/29</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>58852008304898</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -917,7 +965,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E14" t="n">
         <v>2160</v>
@@ -931,10 +979,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/07/29                    </t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>2027/07/29</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>58852008304898</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -953,7 +1005,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E15" t="n">
         <v>2160</v>
@@ -967,10 +1019,14 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/07/29                    </t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>2027/07/29</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>58852008304898</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -989,7 +1045,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E16" t="n">
         <v>480</v>
@@ -1003,10 +1059,14 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/06/12                    </t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>2027/06/12</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>58852008300265</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1025,7 +1085,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E17" t="n">
         <v>480</v>
@@ -1039,10 +1099,14 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/06/12                    </t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>2027/06/12</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>58852008300265</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1061,7 +1125,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E18" t="n">
         <v>480</v>
@@ -1075,10 +1139,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/06/12                    </t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>2027/06/12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>58852008300265</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1097,7 +1165,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E19" t="n">
         <v>480</v>
@@ -1111,10 +1179,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/06/12                    </t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>2027/06/12</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>58852008300265</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1133,7 +1205,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E20" t="n">
         <v>1920</v>
@@ -1147,10 +1219,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/23                    </t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>2027/03/23</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>38801062221197</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1169,7 +1245,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E21" t="n">
         <v>1200</v>
@@ -1183,10 +1259,14 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/04/09                    </t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>2027/04/09</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>38801062221197</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1205,7 +1285,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E22" t="n">
         <v>2160</v>
@@ -1219,10 +1299,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/06/26                    </t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>2027/06/26</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>58852008304898</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1241,7 +1325,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E23" t="n">
         <v>2160</v>
@@ -1255,10 +1339,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/06/26                    </t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>2027/06/26</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>58852008304898</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1277,7 +1365,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E24" t="n">
         <v>2900</v>
@@ -1291,10 +1379,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/07/08                    </t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>2027/07/08</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>58852008510510</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1313,7 +1405,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E25" t="n">
         <v>480</v>
@@ -1327,10 +1419,14 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/06/12                    </t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>2027/06/12</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>58852008300265</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1349,7 +1445,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E26" t="n">
         <v>480</v>
@@ -1363,10 +1459,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/06/12                    </t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>2027/06/12</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>58852008300265</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1385,7 +1485,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E27" t="n">
         <v>480</v>
@@ -1399,10 +1499,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/06/12                    </t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>2027/06/12</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>58852008300265</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1421,7 +1525,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E28" t="n">
         <v>480</v>
@@ -1435,10 +1539,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/06/12                    </t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>2027/06/12</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>58852008300265</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1457,7 +1565,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E29" t="n">
         <v>1200</v>
@@ -1471,10 +1579,14 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/06/26                    </t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>2027/06/26</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>58852008304898</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1493,7 +1605,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="E30" t="n">
         <v>6720</v>
@@ -1507,10 +1619,14 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/16                    </t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>2027/03/16</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>38801062221975</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1529,7 +1645,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E31" t="n">
         <v>1400</v>
@@ -1543,10 +1659,14 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/22                    </t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>2027/03/22</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>68801062332115</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1565,7 +1685,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="E32" t="n">
         <v>700</v>
@@ -1579,10 +1699,14 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/02/28                    </t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>2027/02/28</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>14903333257451</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1601,7 +1725,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="E33" t="n">
         <v>700</v>
@@ -1615,10 +1739,14 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/02/28                    </t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>2027/02/28</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>14903333257451</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1637,7 +1765,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E34" t="n">
         <v>1600</v>
@@ -1651,10 +1779,14 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/22                    </t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>2027/03/22</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>68801062332115</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1673,7 +1805,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E35" t="n">
         <v>200</v>
@@ -1687,10 +1819,14 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/22                    </t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>2027/03/22</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>68801062332115</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1709,7 +1845,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E36" t="n">
         <v>2120</v>
@@ -1723,7 +1859,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031/05/18                    </t>
+          <t>2031/05/18</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -1745,7 +1881,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E37" t="n">
         <v>10</v>
@@ -1759,7 +1895,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028/10/17                    </t>
+          <t>2028/10/17</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -1781,7 +1917,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E38" t="n">
         <v>1200</v>
@@ -1795,10 +1931,14 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/05                    </t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+          <t>2027/03/05</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>68801062863756</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1817,7 +1957,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E39" t="n">
         <v>1200</v>
@@ -1831,10 +1971,14 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/05                    </t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>2027/03/05</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>68801062863756</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1853,7 +1997,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E40" t="n">
         <v>1200</v>
@@ -1867,10 +2011,14 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/05                    </t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>2027/03/05</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>68801062863756</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1889,7 +2037,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E41" t="n">
         <v>1200</v>
@@ -1903,10 +2051,14 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/05                    </t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>2027/03/05</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>68801062863756</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1925,7 +2077,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E42" t="n">
         <v>1200</v>
@@ -1939,10 +2091,14 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/05                    </t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>2027/03/05</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>68801062863756</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1961,7 +2117,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E43" t="n">
         <v>1200</v>
@@ -1975,10 +2131,14 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/05                    </t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+          <t>2027/03/05</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>68801062863756</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1997,7 +2157,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E44" t="n">
         <v>1200</v>
@@ -2011,10 +2171,14 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/05                    </t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>2027/03/05</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>68801062863756</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2033,7 +2197,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E45" t="n">
         <v>1200</v>
@@ -2047,10 +2211,14 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/05                    </t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>2027/03/05</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>68801062863756</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2069,7 +2237,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
         <v>480</v>
@@ -2083,10 +2251,14 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/26                    </t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
+          <t>2027/03/26</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>18801062000781</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2105,7 +2277,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E47" t="n">
         <v>480</v>
@@ -2119,10 +2291,14 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/26                    </t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
+          <t>2027/03/26</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>18801062000781</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2141,7 +2317,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E48" t="n">
         <v>480</v>
@@ -2155,10 +2331,14 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/26                    </t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
+          <t>2027/03/26</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>18801062000781</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2177,7 +2357,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E49" t="n">
         <v>1200</v>
@@ -2191,10 +2371,14 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/05                    </t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+          <t>2027/03/05</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>68801062863756</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2213,7 +2397,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E50" t="n">
         <v>35</v>
@@ -2227,7 +2411,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028/10/17                    </t>
+          <t>2028/10/17</t>
         </is>
       </c>
       <c r="J50" t="inlineStr"/>
@@ -2249,7 +2433,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E51" t="n">
         <v>960</v>
@@ -2263,10 +2447,14 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/04/08                    </t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+          <t>2027/04/08</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>28801062475159</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2285,7 +2473,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E52" t="n">
         <v>7</v>
@@ -2299,10 +2487,14 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028/10/17                    </t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
+          <t>2028/10/17</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>8801062219834</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2321,7 +2513,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
         <v>3</v>
@@ -2335,7 +2527,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/02/03                    </t>
+          <t>2026/02/03</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -2357,7 +2549,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E54" t="n">
         <v>1200</v>
@@ -2371,10 +2563,14 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/05                    </t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
+          <t>2027/03/05</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>68801062863756</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2393,7 +2589,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E55" t="n">
         <v>960</v>
@@ -2407,10 +2603,14 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/04/08                    </t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
+          <t>2027/04/08</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>28801062475159</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2429,7 +2629,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E56" t="n">
         <v>336</v>
@@ -2443,10 +2643,14 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/01                    </t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>2026/12/01</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>18801062899590</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2465,7 +2669,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E57" t="n">
         <v>336</v>
@@ -2479,10 +2683,14 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/01                    </t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+          <t>2026/12/01</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>18801062899590</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2501,7 +2709,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E58" t="n">
         <v>336</v>
@@ -2515,10 +2723,14 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/01                    </t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>2026/12/01</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>18801062899590</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2537,7 +2749,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E59" t="n">
         <v>336</v>
@@ -2551,10 +2763,14 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/01                    </t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+          <t>2026/12/01</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>18801062899590</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2573,7 +2789,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E60" t="n">
         <v>336</v>
@@ -2587,10 +2803,14 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/01                    </t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+          <t>2026/12/01</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>18801062899590</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2609,7 +2829,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E61" t="n">
         <v>960</v>
@@ -2623,10 +2843,14 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/04/08                    </t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
+          <t>2027/04/08</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>28801062475159</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2645,7 +2869,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E62" t="n">
         <v>960</v>
@@ -2659,10 +2883,14 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/04/08                    </t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
+          <t>2027/04/08</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>28801062475159</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2681,7 +2909,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E63" t="n">
         <v>336</v>
@@ -2695,10 +2923,14 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/01                    </t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
+          <t>2026/12/01</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>18801062899590</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2717,7 +2949,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E64" t="n">
         <v>960</v>
@@ -2731,10 +2963,14 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/04/08                    </t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
+          <t>2027/04/08</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>28801062475159</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2753,7 +2989,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E65" t="n">
         <v>336</v>
@@ -2767,10 +3003,14 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/01                    </t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
+          <t>2026/12/01</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>18801062899590</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2789,7 +3029,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E66" t="n">
         <v>336</v>
@@ -2803,10 +3043,14 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/01                    </t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
+          <t>2026/12/01</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>18801062899590</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2825,7 +3069,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E67" t="n">
         <v>336</v>
@@ -2839,10 +3083,14 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/01                    </t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
+          <t>2026/12/01</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>18801062899590</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2861,7 +3109,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E68" t="n">
         <v>336</v>
@@ -2875,10 +3123,14 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/01                    </t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr"/>
+          <t>2026/12/01</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>18801062899590</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2897,7 +3149,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E69" t="n">
         <v>10</v>
@@ -2911,7 +3163,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030/09/11                    </t>
+          <t>2030/09/11</t>
         </is>
       </c>
       <c r="J69" t="inlineStr"/>
@@ -2933,7 +3185,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
         <v>1020</v>
@@ -2947,10 +3199,14 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/02/27                    </t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr"/>
+          <t>2034/02/27</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>8801062311071</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2969,7 +3225,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E71" t="n">
         <v>21</v>
@@ -2983,7 +3239,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031/04/08                    </t>
+          <t>2031/04/08</t>
         </is>
       </c>
       <c r="J71" t="inlineStr"/>
@@ -3005,7 +3261,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="E72" t="n">
         <v>41</v>
@@ -3019,7 +3275,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023/01/06                    </t>
+          <t>2023/01/06</t>
         </is>
       </c>
       <c r="J72" t="inlineStr"/>
@@ -3041,7 +3297,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E73" t="n">
         <v>15</v>
@@ -3055,7 +3311,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028/10/17                    </t>
+          <t>2028/10/17</t>
         </is>
       </c>
       <c r="J73" t="inlineStr"/>
@@ -3077,7 +3333,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E74" t="n">
         <v>35</v>
@@ -3091,7 +3347,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028/10/17                    </t>
+          <t>2028/10/17</t>
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
@@ -3113,7 +3369,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E75" t="n">
         <v>30</v>
@@ -3127,7 +3383,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028/10/17                    </t>
+          <t>2028/10/17</t>
         </is>
       </c>
       <c r="J75" t="inlineStr"/>
@@ -3149,7 +3405,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E76" t="n">
         <v>35</v>
@@ -3163,7 +3419,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028/10/17                    </t>
+          <t>2028/10/17</t>
         </is>
       </c>
       <c r="J76" t="inlineStr"/>
@@ -3185,7 +3441,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E77" t="n">
         <v>35</v>
@@ -3199,7 +3455,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028/10/17                    </t>
+          <t>2028/10/17</t>
         </is>
       </c>
       <c r="J77" t="inlineStr"/>
@@ -3221,7 +3477,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E78" t="n">
         <v>105</v>
@@ -3235,7 +3491,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036/05/07                    </t>
+          <t>2036/05/07</t>
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
@@ -3257,7 +3513,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E79" t="n">
         <v>51</v>
@@ -3271,7 +3527,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029/12/31                    </t>
+          <t>2029/12/31</t>
         </is>
       </c>
       <c r="J79" t="inlineStr"/>
@@ -3293,7 +3549,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E80" t="n">
         <v>17</v>
@@ -3307,7 +3563,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030/12/09                    </t>
+          <t>2030/12/09</t>
         </is>
       </c>
       <c r="J80" t="inlineStr"/>
@@ -3329,7 +3585,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E81" t="n">
         <v>50</v>
@@ -3343,7 +3599,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033/12/25                    </t>
+          <t>2033/12/25</t>
         </is>
       </c>
       <c r="J81" t="inlineStr"/>
@@ -3365,7 +3621,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E82" t="n">
         <v>32</v>
@@ -3379,7 +3635,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030/10/12                    </t>
+          <t>2030/10/12</t>
         </is>
       </c>
       <c r="J82" t="inlineStr"/>
@@ -3401,7 +3657,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E83" t="n">
         <v>35</v>
@@ -3415,7 +3671,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028/10/17                    </t>
+          <t>2028/10/17</t>
         </is>
       </c>
       <c r="J83" t="inlineStr"/>
@@ -3437,7 +3693,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E84" t="n">
         <v>35</v>
@@ -3451,7 +3707,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028/10/17                    </t>
+          <t>2028/10/17</t>
         </is>
       </c>
       <c r="J84" t="inlineStr"/>
@@ -3473,7 +3729,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E85" t="n">
         <v>26</v>
@@ -3487,7 +3743,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024/09/19                    </t>
+          <t>2024/09/19</t>
         </is>
       </c>
       <c r="J85" t="inlineStr"/>
@@ -3509,7 +3765,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E86" t="n">
         <v>26</v>
@@ -3523,7 +3779,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025/04/09                    </t>
+          <t>2025/04/09</t>
         </is>
       </c>
       <c r="J86" t="inlineStr"/>
@@ -3545,7 +3801,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E87" t="n">
         <v>9</v>
@@ -3559,7 +3815,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/01/28                    </t>
+          <t>2026/01/28</t>
         </is>
       </c>
       <c r="J87" t="inlineStr"/>
@@ -3581,7 +3837,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E88" t="n">
         <v>160</v>
@@ -3595,7 +3851,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036/05/07                    </t>
+          <t>2036/05/07</t>
         </is>
       </c>
       <c r="J88" t="inlineStr"/>
@@ -3617,7 +3873,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E89" t="n">
         <v>160</v>
@@ -3631,7 +3887,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036/05/07                    </t>
+          <t>2036/05/07</t>
         </is>
       </c>
       <c r="J89" t="inlineStr"/>
@@ -3653,7 +3909,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E90" t="n">
         <v>9</v>
@@ -3667,7 +3923,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024/09/24                    </t>
+          <t>2024/09/24</t>
         </is>
       </c>
       <c r="J90" t="inlineStr"/>
@@ -3689,7 +3945,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E91" t="n">
         <v>20</v>
@@ -3703,7 +3959,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028/10/17                    </t>
+          <t>2028/10/17</t>
         </is>
       </c>
       <c r="J91" t="inlineStr"/>
@@ -3725,7 +3981,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E92" t="n">
         <v>17</v>
@@ -3739,7 +3995,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023/10/23                    </t>
+          <t>2023/10/23</t>
         </is>
       </c>
       <c r="J92" t="inlineStr"/>
@@ -3761,7 +4017,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E93" t="n">
         <v>30</v>
@@ -3775,7 +4031,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025/02/20                    </t>
+          <t>2025/02/20</t>
         </is>
       </c>
       <c r="J93" t="inlineStr"/>
@@ -3797,7 +4053,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E94" t="n">
         <v>26</v>
@@ -3811,7 +4067,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029/05/06                    </t>
+          <t>2029/05/06</t>
         </is>
       </c>
       <c r="J94" t="inlineStr"/>
@@ -3833,7 +4089,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E95" t="n">
         <v>33</v>
@@ -3847,7 +4103,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028/10/17                    </t>
+          <t>2028/10/17</t>
         </is>
       </c>
       <c r="J95" t="inlineStr"/>
@@ -3869,7 +4125,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E96" t="n">
         <v>35</v>
@@ -3883,7 +4139,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028/10/17                    </t>
+          <t>2028/10/17</t>
         </is>
       </c>
       <c r="J96" t="inlineStr"/>
@@ -3905,7 +4161,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E97" t="n">
         <v>19</v>
@@ -3919,7 +4175,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/04/12                    </t>
+          <t>2027/04/12</t>
         </is>
       </c>
       <c r="J97" t="inlineStr"/>
@@ -3941,7 +4197,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E98" t="n">
         <v>34</v>
@@ -3955,7 +4211,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028/10/17                    </t>
+          <t>2028/10/17</t>
         </is>
       </c>
       <c r="J98" t="inlineStr"/>
@@ -3977,7 +4233,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E99" t="n">
         <v>34</v>
@@ -3991,7 +4247,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/06/30                    </t>
+          <t>2027/06/30</t>
         </is>
       </c>
       <c r="J99" t="inlineStr"/>
@@ -4013,7 +4269,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E100" t="n">
         <v>26</v>
@@ -4027,7 +4283,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032/03/02                    </t>
+          <t>2032/03/02</t>
         </is>
       </c>
       <c r="J100" t="inlineStr"/>
@@ -4049,7 +4305,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
         <v>94</v>
@@ -4063,10 +4319,14 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033/06/14                    </t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr"/>
+          <t>2033/06/14</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>4712834453902</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4085,7 +4345,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E102" t="n">
         <v>70</v>
@@ -4099,10 +4359,14 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/10/25                    </t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr"/>
+          <t>2034/10/25</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>4712834459140</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4121,7 +4385,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E103" t="n">
         <v>70</v>
@@ -4135,10 +4399,14 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/10/25                    </t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr"/>
+          <t>2034/10/25</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>4712834459140</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4157,7 +4425,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E104" t="n">
         <v>587</v>
@@ -4171,10 +4439,14 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036/01/02                    </t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr"/>
+          <t>2036/01/02</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>4712834459416</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4193,7 +4465,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E105" t="n">
         <v>720</v>
@@ -4207,10 +4479,14 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/01                    </t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr"/>
+          <t>2026/12/01</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>18801062899613</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4229,7 +4505,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E106" t="n">
         <v>720</v>
@@ -4243,10 +4519,14 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/01                    </t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr"/>
+          <t>2026/12/01</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>18801062899613</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4265,7 +4545,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E107" t="n">
         <v>480</v>
@@ -4279,10 +4559,14 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/26                    </t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr"/>
+          <t>2027/03/26</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>18801062000781</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4301,7 +4585,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E108" t="n">
         <v>2000</v>
@@ -4315,7 +4599,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036/03/18                    </t>
+          <t>2036/03/18</t>
         </is>
       </c>
       <c r="J108" t="inlineStr"/>
@@ -4337,7 +4621,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E109" t="n">
         <v>128</v>
@@ -4351,10 +4635,14 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036/01/02                    </t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr"/>
+          <t>2036/01/02</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>4712834459393</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4373,7 +4661,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E110" t="n">
         <v>18</v>
@@ -4387,10 +4675,14 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033/11/10                    </t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr"/>
+          <t>2033/11/10</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>4712834459010</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4409,7 +4701,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
         <v>75</v>
@@ -4423,7 +4715,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/05/25                    </t>
+          <t>2034/05/25</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -4445,7 +4737,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" t="n">
         <v>75</v>
@@ -4459,7 +4751,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/05/25                    </t>
+          <t>2034/05/25</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -4481,7 +4773,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E113" t="n">
         <v>2160</v>
@@ -4495,10 +4787,14 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/06/05                    </t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr"/>
+          <t>2027/06/05</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>58852008300784</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4517,7 +4813,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114" t="n">
         <v>358</v>
@@ -4531,7 +4827,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/02/21                    </t>
+          <t>2034/02/21</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
@@ -4553,7 +4849,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E115" t="n">
         <v>2160</v>
@@ -4567,10 +4863,14 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/06/05                    </t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr"/>
+          <t>2027/06/05</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>58852008300784</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4589,7 +4889,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E116" t="n">
         <v>2160</v>
@@ -4603,10 +4903,14 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/06/05                    </t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr"/>
+          <t>2027/06/05</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>58852008300784</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4625,7 +4929,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E117" t="n">
         <v>2160</v>
@@ -4639,10 +4943,14 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/06/05                    </t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr"/>
+          <t>2027/06/05</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>58852008300784</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4661,7 +4969,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
         <v>18</v>
@@ -4675,10 +4983,14 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035/10/14                    </t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr"/>
+          <t>2035/10/14</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>4712834459324</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4697,7 +5009,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E119" t="n">
         <v>2160</v>
@@ -4711,10 +5023,14 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/06/04                    </t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr"/>
+          <t>2027/06/04</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>58852008300784</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4733,7 +5049,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E120" t="n">
         <v>2160</v>
@@ -4747,10 +5063,14 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/06/05                    </t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr"/>
+          <t>2027/06/05</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>58852008300784</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4769,7 +5089,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E121" t="n">
         <v>1424</v>
@@ -4783,10 +5103,14 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032/05/05                    </t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr"/>
+          <t>2032/05/05</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>4712834453643</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4805,7 +5129,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E122" t="n">
         <v>900</v>
@@ -4819,10 +5143,14 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036/03/18                    </t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr"/>
+          <t>2036/03/18</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>4712834459461</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4841,7 +5169,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E123" t="n">
         <v>616</v>
@@ -4855,10 +5183,14 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032/05/05                    </t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr"/>
+          <t>2032/05/05</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>4712834453643</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4877,7 +5209,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E124" t="n">
         <v>504</v>
@@ -4891,10 +5223,14 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/08/16                    </t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr"/>
+          <t>2034/08/16</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>4712834453896</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4913,7 +5249,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E125" t="n">
         <v>1800</v>
@@ -4927,10 +5263,14 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/08/16                    </t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr"/>
+          <t>2034/08/16</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>4712834453896</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4949,7 +5289,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E126" t="n">
         <v>1184</v>
@@ -4963,10 +5303,14 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028/08/11                    </t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr"/>
+          <t>2028/08/11</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>4712834459485</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4985,7 +5329,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E127" t="n">
         <v>5400</v>
@@ -4999,10 +5343,14 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028/08/11                    </t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr"/>
+          <t>2028/08/11</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>4712834459485</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5021,7 +5369,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E128" t="n">
         <v>393</v>
@@ -5035,7 +5383,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036/02/04                    </t>
+          <t>2036/02/04</t>
         </is>
       </c>
       <c r="J128" t="inlineStr"/>
@@ -5057,7 +5405,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E129" t="n">
         <v>496</v>
@@ -5071,10 +5419,14 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/10/18                    </t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr"/>
+          <t>2034/10/18</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>4712834459119</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5093,7 +5445,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E130" t="n">
         <v>160</v>
@@ -5107,10 +5459,14 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/06/26                    </t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr"/>
+          <t>2034/06/26</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>4712834459119</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5129,7 +5485,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E131" t="n">
         <v>1200</v>
@@ -5143,10 +5499,14 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/05                    </t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr"/>
+          <t>2027/03/05</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>68801062863756</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5165,7 +5525,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E132" t="n">
         <v>2160</v>
@@ -5179,10 +5539,14 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/08/14                    </t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr"/>
+          <t>2027/08/14</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>58852008305673</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5201,7 +5565,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E133" t="n">
         <v>336</v>
@@ -5215,10 +5579,14 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/01                    </t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr"/>
+          <t>2026/12/01</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>18801062899590</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5237,7 +5605,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E134" t="n">
         <v>336</v>
@@ -5251,10 +5619,14 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/01                    </t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr"/>
+          <t>2026/12/01</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>18801062899590</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5273,7 +5645,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E135" t="n">
         <v>338</v>
@@ -5287,10 +5659,14 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030/08/31                    </t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr"/>
+          <t>2030/08/31</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>4712834459324</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5309,7 +5685,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E136" t="n">
         <v>1181</v>
@@ -5323,10 +5699,14 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/08/06                    </t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr"/>
+          <t>2034/08/06</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>4712834453896</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5345,7 +5725,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E137" t="n">
         <v>1629</v>
@@ -5359,7 +5739,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036/12/31                    </t>
+          <t>2036/12/31</t>
         </is>
       </c>
       <c r="J137" t="inlineStr"/>
@@ -5381,7 +5761,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E138" t="n">
         <v>395</v>
@@ -5395,7 +5775,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036/05/25                    </t>
+          <t>2036/05/25</t>
         </is>
       </c>
       <c r="J138" t="inlineStr"/>
@@ -5417,7 +5797,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E139" t="n">
         <v>480</v>
@@ -5431,10 +5811,14 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/01/10                    </t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr"/>
+          <t>2027/01/10</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>08935341301238</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5453,7 +5837,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E140" t="n">
         <v>336</v>
@@ -5467,10 +5851,14 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/01/23                    </t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr"/>
+          <t>2027/01/23</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>04712834457429</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5489,7 +5877,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E141" t="n">
         <v>336</v>
@@ -5503,10 +5891,14 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/01/23                    </t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr"/>
+          <t>2027/01/23</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>04712834457429</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5525,7 +5917,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E142" t="n">
         <v>718</v>
@@ -5539,7 +5931,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/31                    </t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="J142" t="inlineStr"/>
@@ -5561,7 +5953,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E143" t="n">
         <v>1200</v>
@@ -5575,10 +5967,14 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/03/05                    </t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr"/>
+          <t>2027/03/05</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>68801062863756</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5597,7 +5993,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E144" t="n">
         <v>1200</v>
@@ -5611,10 +6007,14 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/01/14                    </t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr"/>
+          <t>2027/01/14</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>68801062863756</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5633,7 +6033,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E145" t="n">
         <v>2160</v>
@@ -5647,10 +6047,14 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/08/14                    </t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr"/>
+          <t>2027/08/14</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>58852008305673</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5669,7 +6073,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E146" t="n">
         <v>336</v>
@@ -5683,10 +6087,14 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/01/23                    </t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr"/>
+          <t>2027/01/23</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>04712834457429</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5705,7 +6113,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E147" t="n">
         <v>395</v>
@@ -5719,7 +6127,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036/05/25                    </t>
+          <t>2036/05/25</t>
         </is>
       </c>
       <c r="J147" t="inlineStr"/>
@@ -5755,7 +6163,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036/01/30                    </t>
+          <t>2036/01/30</t>
         </is>
       </c>
       <c r="J148" t="inlineStr"/>
@@ -5777,7 +6185,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E149" t="n">
         <v>295</v>
@@ -5791,10 +6199,14 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036/03/20                    </t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr"/>
+          <t>2036/03/20</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>4712834459454</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5827,7 +6239,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036/01/30                    </t>
+          <t>2036/01/30</t>
         </is>
       </c>
       <c r="J150" t="inlineStr"/>
@@ -5849,7 +6261,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E151" t="n">
         <v>518</v>
@@ -5863,10 +6275,14 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030/08/31                    </t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr"/>
+          <t>2030/08/31</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>4712834459324</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5899,7 +6315,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031/02/01                    </t>
+          <t>2031/02/01</t>
         </is>
       </c>
       <c r="J152" t="inlineStr"/>
@@ -5935,10 +6351,14 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035/04/11                    </t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr"/>
+          <t>2035/04/11</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>4712834459256</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5957,7 +6377,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E154" t="n">
         <v>203</v>
@@ -5971,10 +6391,14 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035/08/18                    </t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr"/>
+          <t>2035/08/18</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>4712834459263</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5993,7 +6417,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E155" t="n">
         <v>3317</v>
@@ -6007,7 +6431,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030/01/31                    </t>
+          <t>2030/01/31</t>
         </is>
       </c>
       <c r="J155" t="inlineStr"/>
@@ -6029,7 +6453,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E156" t="n">
         <v>1526</v>
@@ -6043,10 +6467,14 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033/05/02                    </t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr"/>
+          <t>2033/05/02</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>4712834453865</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6065,7 +6493,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157" t="n">
         <v>88</v>
@@ -6079,10 +6507,14 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/11/26                    </t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr"/>
+          <t>2034/11/26</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>4712834459157</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6101,7 +6533,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="E158" t="n">
         <v>896</v>
@@ -6115,10 +6547,14 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030/08/31                    </t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr"/>
+          <t>2030/08/31</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>4712834459324</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6137,7 +6573,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E159" t="n">
         <v>570</v>
@@ -6151,7 +6587,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031/01/31                    </t>
+          <t>2031/01/31</t>
         </is>
       </c>
       <c r="J159" t="inlineStr"/>
@@ -6173,7 +6609,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E160" t="n">
         <v>336</v>
@@ -6187,10 +6623,14 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/01/23                    </t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr"/>
+          <t>2027/01/23</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>04712834457429</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6209,7 +6649,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E161" t="n">
         <v>336</v>
@@ -6223,10 +6663,14 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/01/23                    </t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr"/>
+          <t>2027/01/23</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>04712834457429</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6245,7 +6689,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E162" t="n">
         <v>177</v>
@@ -6259,10 +6703,14 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/04/17                    </t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr"/>
+          <t>2034/04/17</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>4712834459140</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6281,7 +6729,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E163" t="n">
         <v>418</v>
@@ -6295,10 +6743,14 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/04/17                    </t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr"/>
+          <t>2034/04/17</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>4712834459140</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6317,7 +6769,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E164" t="n">
         <v>61</v>
@@ -6331,10 +6783,14 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/11/02                    </t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr"/>
+          <t>2034/11/02</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>4712834459065</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6367,7 +6823,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/12/06                    </t>
+          <t>2034/12/06</t>
         </is>
       </c>
       <c r="J165" t="inlineStr"/>
@@ -6403,7 +6859,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/12/06                    </t>
+          <t>2034/12/06</t>
         </is>
       </c>
       <c r="J166" t="inlineStr"/>
@@ -6425,7 +6881,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E167" t="n">
         <v>6</v>
@@ -6439,10 +6895,14 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035/02/07                    </t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr"/>
+          <t>2035/02/07</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>4712834459225</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6461,7 +6921,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E168" t="n">
         <v>2081</v>
@@ -6475,10 +6935,14 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032/05/05                    </t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr"/>
+          <t>2032/05/05</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>4712834453643</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6497,7 +6961,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E169" t="n">
         <v>1800</v>
@@ -6511,10 +6975,14 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/08/07                    </t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr"/>
+          <t>2034/08/07</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>4712834453896</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6533,7 +7001,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E170" t="n">
         <v>540</v>
@@ -6547,10 +7015,14 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/11/02                    </t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr"/>
+          <t>2034/11/02</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>4712834459065</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6569,7 +7041,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E171" t="n">
         <v>540</v>
@@ -6583,10 +7055,14 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034/11/02                    </t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr"/>
+          <t>2034/11/02</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>4712834459065</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6605,7 +7081,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E172" t="n">
         <v>4320</v>
@@ -6619,10 +7095,14 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027/08/15                    </t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr"/>
+          <t>2027/08/15</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>58852008305673</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6641,7 +7121,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E173" t="n">
         <v>333</v>
@@ -6655,10 +7135,14 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/11/26                    </t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr"/>
+          <t>2026/11/26</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>48801062267796</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6677,7 +7161,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E174" t="n">
         <v>648</v>
@@ -6691,10 +7175,14 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/11/26                    </t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr"/>
+          <t>2026/11/26</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>48801062267796</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6713,7 +7201,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E175" t="n">
         <v>648</v>
@@ -6727,10 +7215,14 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/11/26                    </t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr"/>
+          <t>2026/11/26</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>48801062267796</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6749,7 +7241,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E176" t="n">
         <v>648</v>
@@ -6763,10 +7255,14 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/11/26                    </t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr"/>
+          <t>2026/11/26</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>48801062267796</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6785,7 +7281,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E177" t="n">
         <v>648</v>
@@ -6799,10 +7295,14 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/11/26                    </t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr"/>
+          <t>2026/11/26</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>48801062267796</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6821,7 +7321,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E178" t="n">
         <v>648</v>
@@ -6835,10 +7335,14 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/11/26                    </t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr"/>
+          <t>2026/11/26</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>48801062267796</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6857,7 +7361,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E179" t="n">
         <v>648</v>
@@ -6871,10 +7375,14 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/11/26                    </t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr"/>
+          <t>2026/11/26</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>48801062267796</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6893,7 +7401,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E180" t="n">
         <v>648</v>
@@ -6907,10 +7415,14 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/11/26                    </t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr"/>
+          <t>2026/11/26</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>48801062267796</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6929,7 +7441,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E181" t="n">
         <v>648</v>
@@ -6943,10 +7455,14 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/11/26                    </t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr"/>
+          <t>2026/11/26</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>48801062267796</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6965,7 +7481,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E182" t="n">
         <v>648</v>
@@ -6979,10 +7495,14 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/11/26                    </t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr"/>
+          <t>2026/11/26</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>48801062267796</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7001,7 +7521,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E183" t="n">
         <v>648</v>
@@ -7015,10 +7535,14 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/11/26                    </t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr"/>
+          <t>2026/11/26</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>48801062267796</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7037,7 +7561,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E184" t="n">
         <v>648</v>
@@ -7051,10 +7575,14 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/11/25                    </t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr"/>
+          <t>2026/11/25</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>48801062267796</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7073,7 +7601,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E185" t="n">
         <v>648</v>
@@ -7087,10 +7615,14 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/11/25                    </t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr"/>
+          <t>2026/11/25</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>48801062267796</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7109,7 +7641,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E186" t="n">
         <v>648</v>
@@ -7123,10 +7655,14 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/11/25                    </t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr"/>
+          <t>2026/11/25</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>48801062267796</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7145,7 +7681,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E187" t="n">
         <v>648</v>
@@ -7159,10 +7695,14 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/11/25                    </t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr"/>
+          <t>2026/11/25</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>48801062267796</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7181,7 +7721,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E188" t="n">
         <v>648</v>
@@ -7195,10 +7735,14 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/11/26                    </t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr"/>
+          <t>2026/11/26</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>48801062267796</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7217,7 +7761,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E189" t="n">
         <v>648</v>
@@ -7231,10 +7775,14 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/11/25                    </t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr"/>
+          <t>2026/11/25</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>48801062267796</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7253,7 +7801,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E190" t="n">
         <v>648</v>
@@ -7267,10 +7815,14 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/11/26                    </t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr"/>
+          <t>2026/11/26</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>48801062267796</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7289,7 +7841,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E191" t="n">
         <v>648</v>
@@ -7303,10 +7855,14 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/09                    </t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr"/>
+          <t>2026/12/09</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>48801062641237</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7325,7 +7881,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E192" t="n">
         <v>648</v>
@@ -7339,10 +7895,14 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/09                    </t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr"/>
+          <t>2026/12/09</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>48801062641237</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7361,7 +7921,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E193" t="n">
         <v>648</v>
@@ -7375,10 +7935,14 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/09                    </t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr"/>
+          <t>2026/12/09</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>48801062641237</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7397,7 +7961,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E194" t="n">
         <v>648</v>
@@ -7411,10 +7975,14 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/09                    </t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr"/>
+          <t>2026/12/09</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>48801062641237</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7433,7 +8001,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E195" t="n">
         <v>648</v>
@@ -7447,10 +8015,14 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/09                    </t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr"/>
+          <t>2026/12/09</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>48801062641237</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7469,7 +8041,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E196" t="n">
         <v>648</v>
@@ -7483,10 +8055,14 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/09                    </t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr"/>
+          <t>2026/12/09</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>48801062641237</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7505,7 +8081,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E197" t="n">
         <v>648</v>
@@ -7519,10 +8095,14 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/09                    </t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr"/>
+          <t>2026/12/09</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>48801062641237</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7541,7 +8121,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E198" t="n">
         <v>648</v>
@@ -7555,10 +8135,14 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/09                    </t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr"/>
+          <t>2026/12/09</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>48801062641237</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7577,7 +8161,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E199" t="n">
         <v>648</v>
@@ -7591,10 +8175,14 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/09                    </t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr"/>
+          <t>2026/12/09</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>48801062641237</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7613,7 +8201,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E200" t="n">
         <v>648</v>
@@ -7627,10 +8215,14 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/09                    </t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr"/>
+          <t>2026/12/09</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>48801062641237</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7649,7 +8241,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E201" t="n">
         <v>648</v>
@@ -7663,10 +8255,14 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/09                    </t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr"/>
+          <t>2026/12/09</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>48801062641237</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7685,7 +8281,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E202" t="n">
         <v>648</v>
@@ -7699,10 +8295,14 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/09                    </t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr"/>
+          <t>2026/12/09</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>48801062641237</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7721,7 +8321,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E203" t="n">
         <v>288</v>
@@ -7735,10 +8335,14 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/17                    </t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr"/>
+          <t>2026/12/17</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>48801062641237</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7757,7 +8361,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E204" t="n">
         <v>648</v>
@@ -7771,10 +8375,14 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/09                    </t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr"/>
+          <t>2026/12/09</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>48801062641237</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7793,7 +8401,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E205" t="n">
         <v>648</v>
@@ -7807,10 +8415,14 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/17                    </t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr"/>
+          <t>2026/12/17</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>48801062641237</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7829,7 +8441,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E206" t="n">
         <v>648</v>
@@ -7843,10 +8455,14 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/17                    </t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr"/>
+          <t>2026/12/17</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>48801062641237</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7865,7 +8481,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E207" t="n">
         <v>648</v>
@@ -7879,10 +8495,14 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/09                    </t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr"/>
+          <t>2026/12/09</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>48801062641237</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7901,7 +8521,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="E208" t="n">
         <v>549</v>
@@ -7915,10 +8535,14 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026/12/17                    </t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr"/>
+          <t>2026/12/17</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>48801062641237</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
